--- a/tame_output/ON/bt/strategyON_20231204.xlsx
+++ b/tame_output/ON/bt/strategyON_20231204.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-107.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,32 +977,32 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>440.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,15 +1107,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-86.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-156.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-76.1%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,15 +1413,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>112.8%</t>
+          <t>101.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-22.1%</t>
         </is>
       </c>
     </row>
@@ -41743,16 +41743,16 @@
         <v>2.941291882277773</v>
       </c>
       <c r="D1749" t="n">
-        <v>0.9103370657437468</v>
+        <v>0.5195524192447896</v>
       </c>
       <c r="E1749" t="n">
-        <v>3.305070284261525</v>
+        <v>3.148756425661942</v>
       </c>
       <c r="F1749" t="n">
-        <v>1.701477389950992</v>
+        <v>1.310692743452034</v>
       </c>
       <c r="G1749" t="n">
-        <v>3.962178316248369</v>
+        <v>3.727707528348995</v>
       </c>
     </row>
     <row r="1750">
@@ -41766,16 +41766,16 @@
         <v>2.950500122107244</v>
       </c>
       <c r="D1750" t="n">
-        <v>0.9143859137610523</v>
+        <v>0.523601267262095</v>
       </c>
       <c r="E1750" t="n">
-        <v>3.315898063297918</v>
+        <v>3.159584204698335</v>
       </c>
       <c r="F1750" t="n">
-        <v>1.705526237968297</v>
+        <v>1.314741591469339</v>
       </c>
       <c r="G1750" t="n">
-        <v>3.973815864888224</v>
+        <v>3.73934507698885</v>
       </c>
     </row>
     <row r="1751">
@@ -41789,16 +41789,16 @@
         <v>2.950191610492619</v>
       </c>
       <c r="D1751" t="n">
-        <v>0.9140202027200215</v>
+        <v>0.5232355562210642</v>
       </c>
       <c r="E1751" t="n">
-        <v>3.315443267266881</v>
+        <v>3.159129408667298</v>
       </c>
       <c r="F1751" t="n">
-        <v>1.704655743751013</v>
+        <v>1.313871097252056</v>
       </c>
       <c r="G1751" t="n">
-        <v>3.972985056743229</v>
+        <v>3.738514268843855</v>
       </c>
     </row>
     <row r="1752">
@@ -41812,16 +41812,16 @@
         <v>2.953840430523644</v>
       </c>
       <c r="D1752" t="n">
-        <v>0.9136467897090208</v>
+        <v>0.5228621432100635</v>
       </c>
       <c r="E1752" t="n">
-        <v>3.318942722093505</v>
+        <v>3.162628863493922</v>
       </c>
       <c r="F1752" t="n">
-        <v>1.704655743751013</v>
+        <v>1.313871097252056</v>
       </c>
       <c r="G1752" t="n">
-        <v>3.976633876774254</v>
+        <v>3.742163088874879</v>
       </c>
     </row>
     <row r="1753">
@@ -41835,16 +41835,16 @@
         <v>2.959094075792072</v>
       </c>
       <c r="D1753" t="n">
-        <v>0.9191577341757343</v>
+        <v>0.528373087676777</v>
       </c>
       <c r="E1753" t="n">
-        <v>3.326400745148618</v>
+        <v>3.170086886549035</v>
       </c>
       <c r="F1753" t="n">
-        <v>1.704655743751013</v>
+        <v>1.313871097252056</v>
       </c>
       <c r="G1753" t="n">
-        <v>3.981887522042681</v>
+        <v>3.747416734143307</v>
       </c>
     </row>
     <row r="1754">
@@ -41858,16 +41858,16 @@
         <v>2.957874679524909</v>
       </c>
       <c r="D1754" t="n">
-        <v>0.9194283115170602</v>
+        <v>0.5286436650181029</v>
       </c>
       <c r="E1754" t="n">
-        <v>3.325289579817986</v>
+        <v>3.168975721218403</v>
       </c>
       <c r="F1754" t="n">
-        <v>1.705152270053664</v>
+        <v>1.314367623554707</v>
       </c>
       <c r="G1754" t="n">
-        <v>3.980966041557109</v>
+        <v>3.746495253657734</v>
       </c>
     </row>
     <row r="1755">
@@ -41881,16 +41881,16 @@
         <v>2.95420083304114</v>
       </c>
       <c r="D1755" t="n">
-        <v>0.9274134798988046</v>
+        <v>0.5366288333998473</v>
       </c>
       <c r="E1755" t="n">
-        <v>3.324809800686915</v>
+        <v>3.168495942087332</v>
       </c>
       <c r="F1755" t="n">
-        <v>1.707379816090441</v>
+        <v>1.316595169591483</v>
       </c>
       <c r="G1755" t="n">
-        <v>3.978628722695406</v>
+        <v>3.744157934796032</v>
       </c>
     </row>
     <row r="1756">
@@ -41904,16 +41904,16 @@
         <v>2.969006534107256</v>
       </c>
       <c r="D1756" t="n">
-        <v>0.9165271161277609</v>
+        <v>0.5257424696288037</v>
       </c>
       <c r="E1756" t="n">
-        <v>3.335260956244614</v>
+        <v>3.178947097645031</v>
       </c>
       <c r="F1756" t="n">
-        <v>1.707379816090441</v>
+        <v>1.316595169591483</v>
       </c>
       <c r="G1756" t="n">
-        <v>3.993434423761522</v>
+        <v>3.758963635862148</v>
       </c>
     </row>
     <row r="1757">
@@ -41927,16 +41927,16 @@
         <v>2.968547780644436</v>
       </c>
       <c r="D1757" t="n">
-        <v>0.9246442560854061</v>
+        <v>0.5338596095864488</v>
       </c>
       <c r="E1757" t="n">
-        <v>3.338049058764852</v>
+        <v>3.181735200165269</v>
       </c>
       <c r="F1757" t="n">
-        <v>1.707379816090441</v>
+        <v>1.316595169591483</v>
       </c>
       <c r="G1757" t="n">
-        <v>3.992975670298702</v>
+        <v>3.758504882399328</v>
       </c>
     </row>
     <row r="1758">
@@ -41950,16 +41950,16 @@
         <v>2.965146865274802</v>
       </c>
       <c r="D1758" t="n">
-        <v>0.9291536043111913</v>
+        <v>0.538368957812234</v>
       </c>
       <c r="E1758" t="n">
-        <v>3.336451882685532</v>
+        <v>3.180138024085949</v>
       </c>
       <c r="F1758" t="n">
-        <v>1.707379816090441</v>
+        <v>1.316595169591483</v>
       </c>
       <c r="G1758" t="n">
-        <v>3.989574754929069</v>
+        <v>3.755103967029694</v>
       </c>
     </row>
     <row r="1759">
@@ -41973,16 +41973,16 @@
         <v>2.964689051375926</v>
       </c>
       <c r="D1759" t="n">
-        <v>0.9188464786537562</v>
+        <v>0.528061832154799</v>
       </c>
       <c r="E1759" t="n">
-        <v>3.331871218523682</v>
+        <v>3.175557359924099</v>
       </c>
       <c r="F1759" t="n">
-        <v>1.700381433775587</v>
+        <v>1.30959678727663</v>
       </c>
       <c r="G1759" t="n">
-        <v>3.98491791164128</v>
+        <v>3.750447123741906</v>
       </c>
     </row>
     <row r="1760">
@@ -41996,16 +41996,16 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>0.8706038297680443</v>
+        <v>0.479819183269087</v>
       </c>
       <c r="E1760" t="n">
-        <v>3.340359816927575</v>
+        <v>3.184045958327992</v>
       </c>
       <c r="F1760" t="n">
-        <v>1.700381433775587</v>
+        <v>1.30959678727663</v>
       </c>
       <c r="G1760" t="n">
-        <v>4.012703569599458</v>
+        <v>3.778232781700083</v>
       </c>
     </row>
     <row r="1761">
@@ -42019,16 +42019,16 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>0.877701830735546</v>
+        <v>0.4869171842365886</v>
       </c>
       <c r="E1761" t="n">
-        <v>3.360973726356036</v>
+        <v>3.204659867756452</v>
       </c>
       <c r="F1761" t="n">
-        <v>1.700488631886963</v>
+        <v>1.309703985388006</v>
       </c>
       <c r="G1761" t="n">
-        <v>4.030542597507743</v>
+        <v>3.796071809608369</v>
       </c>
     </row>
     <row r="1762">
@@ -42042,16 +42042,16 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>0.8789048970316524</v>
+        <v>0.488120250532695</v>
       </c>
       <c r="E1762" t="n">
-        <v>3.361928512555519</v>
+        <v>3.205614653955936</v>
       </c>
       <c r="F1762" t="n">
-        <v>1.700488631886963</v>
+        <v>1.309703985388006</v>
       </c>
       <c r="G1762" t="n">
-        <v>4.031016157188784</v>
+        <v>3.79654536928941</v>
       </c>
     </row>
     <row r="1763">
@@ -42065,16 +42065,16 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>0.8812579443648979</v>
+        <v>0.4904732978659405</v>
       </c>
       <c r="E1763" t="n">
-        <v>3.368209103625714</v>
+        <v>3.211895245026131</v>
       </c>
       <c r="F1763" t="n">
-        <v>1.702841679220209</v>
+        <v>1.312057032721251</v>
       </c>
       <c r="G1763" t="n">
-        <v>4.037767357725628</v>
+        <v>3.803296569826254</v>
       </c>
     </row>
     <row r="1764">
@@ -42088,16 +42088,16 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>0.8823742263561241</v>
+        <v>0.4915895798571667</v>
       </c>
       <c r="E1764" t="n">
-        <v>3.383232641258254</v>
+        <v>3.226918782658671</v>
       </c>
       <c r="F1764" t="n">
-        <v>1.703957961211435</v>
+        <v>1.313173314712477</v>
       </c>
       <c r="G1764" t="n">
-        <v>4.053014151756414</v>
+        <v>3.818543363857039</v>
       </c>
     </row>
     <row r="1765">
@@ -42111,16 +42111,16 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>0.8861121824171795</v>
+        <v>0.4953275359182221</v>
       </c>
       <c r="E1765" t="n">
-        <v>3.384652804546323</v>
+        <v>3.22833894594674</v>
       </c>
       <c r="F1765" t="n">
-        <v>1.70633441349206</v>
+        <v>1.315549766993102</v>
       </c>
       <c r="G1765" t="n">
-        <v>4.054365003988436</v>
+        <v>3.819894216089061</v>
       </c>
     </row>
     <row r="1766">
@@ -42134,16 +42134,16 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>0.8946093280783127</v>
+        <v>0.5038246815793553</v>
       </c>
       <c r="E1766" t="n">
-        <v>3.386367087308871</v>
+        <v>3.230053228709288</v>
       </c>
       <c r="F1766" t="n">
-        <v>1.70633441349206</v>
+        <v>1.315549766993102</v>
       </c>
       <c r="G1766" t="n">
-        <v>4.05268042848653</v>
+        <v>3.818209640587156</v>
       </c>
     </row>
     <row r="1767">
@@ -42157,16 +42157,16 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>0.8949172881630374</v>
+        <v>0.5041326416640799</v>
       </c>
       <c r="E1767" t="n">
-        <v>3.390878847023607</v>
+        <v>3.234564988424024</v>
       </c>
       <c r="F1767" t="n">
-        <v>1.70751612758476</v>
+        <v>1.316731481085802</v>
       </c>
       <c r="G1767" t="n">
-        <v>4.057778032622997</v>
+        <v>3.823307244723622</v>
       </c>
     </row>
     <row r="1768">
@@ -42180,16 +42180,16 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>0.8966990505336287</v>
+        <v>0.5059144040346713</v>
       </c>
       <c r="E1768" t="n">
-        <v>3.393251849148718</v>
+        <v>3.236937990549135</v>
       </c>
       <c r="F1768" t="n">
-        <v>1.70751612758476</v>
+        <v>1.316731481085802</v>
       </c>
       <c r="G1768" t="n">
-        <v>4.059438329799871</v>
+        <v>3.824967541900496</v>
       </c>
     </row>
     <row r="1769">
@@ -42203,16 +42203,16 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>0.8926216953965374</v>
+        <v>0.5018370488975799</v>
       </c>
       <c r="E1769" t="n">
-        <v>3.406655077357572</v>
+        <v>3.250341218757989</v>
       </c>
       <c r="F1769" t="n">
-        <v>1.70751612758476</v>
+        <v>1.316731481085802</v>
       </c>
       <c r="G1769" t="n">
-        <v>4.074472500063561</v>
+        <v>3.840001712164187</v>
       </c>
     </row>
     <row r="1770">
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>0.9026137763229465</v>
+        <v>0.511829129823989</v>
       </c>
       <c r="E1770" t="n">
-        <v>3.408966344392269</v>
+        <v>3.252652485792686</v>
       </c>
       <c r="F1770" t="n">
-        <v>1.717508208511169</v>
+        <v>1.326723562012211</v>
       </c>
       <c r="G1770" t="n">
-        <v>4.07878218328354</v>
+        <v>3.844311395384165</v>
       </c>
     </row>
     <row r="1771">
@@ -42249,16 +42249,16 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>0.9020580212669087</v>
+        <v>0.5112733747679512</v>
       </c>
       <c r="E1771" t="n">
-        <v>3.411645852266445</v>
+        <v>3.255331993666862</v>
       </c>
       <c r="F1771" t="n">
-        <v>1.715900794750091</v>
+        <v>1.325116148251133</v>
       </c>
       <c r="G1771" t="n">
-        <v>4.080719544923484</v>
+        <v>3.84624875702411</v>
       </c>
     </row>
     <row r="1772">
@@ -42272,16 +42272,16 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>0.8988436688535972</v>
+        <v>0.5080590223546397</v>
       </c>
       <c r="E1772" t="n">
-        <v>3.415885100440267</v>
+        <v>3.259571241840684</v>
       </c>
       <c r="F1772" t="n">
-        <v>1.715900794750091</v>
+        <v>1.325116148251133</v>
       </c>
       <c r="G1772" t="n">
-        <v>4.086244534062631</v>
+        <v>3.851773746163257</v>
       </c>
     </row>
     <row r="1773">
@@ -42295,16 +42295,16 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>0.8818354234509878</v>
+        <v>0.4910507769520303</v>
       </c>
       <c r="E1773" t="n">
-        <v>3.410159374916955</v>
+        <v>3.253845516317372</v>
       </c>
       <c r="F1773" t="n">
-        <v>1.718899929763065</v>
+        <v>1.328115283264107</v>
       </c>
       <c r="G1773" t="n">
-        <v>4.089121587708147</v>
+        <v>3.854650799808772</v>
       </c>
     </row>
     <row r="1774">
@@ -42318,16 +42318,16 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>0.9007951459023423</v>
+        <v>0.5100104994033848</v>
       </c>
       <c r="E1774" t="n">
-        <v>3.418493126068769</v>
+        <v>3.262179267469187</v>
       </c>
       <c r="F1774" t="n">
-        <v>1.718899929763065</v>
+        <v>1.328115283264107</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.08987144987942</v>
+        <v>3.855400661980045</v>
       </c>
     </row>
     <row r="1775">
@@ -42341,16 +42341,16 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>0.902029870505151</v>
+        <v>0.5112452240061935</v>
       </c>
       <c r="E1775" t="n">
-        <v>3.417222613373474</v>
+        <v>3.260908754773891</v>
       </c>
       <c r="F1775" t="n">
-        <v>1.718899929763065</v>
+        <v>1.328115283264107</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.088107047343001</v>
+        <v>3.853636259443626</v>
       </c>
     </row>
     <row r="1776">
@@ -42364,16 +42364,16 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>0.8919956066815024</v>
+        <v>0.5012109601825449</v>
       </c>
       <c r="E1776" t="n">
-        <v>3.416776517680876</v>
+        <v>3.260462659081294</v>
       </c>
       <c r="F1776" t="n">
-        <v>1.718899929763065</v>
+        <v>1.328115283264107</v>
       </c>
       <c r="G1776" t="n">
-        <v>4.091674657179863</v>
+        <v>3.857203869280488</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>0.8869566083836355</v>
+        <v>0.496171961884678</v>
       </c>
       <c r="E1777" t="n">
-        <v>3.438742880251338</v>
+        <v>3.282429021651756</v>
       </c>
       <c r="F1777" t="n">
-        <v>1.713860931465198</v>
+        <v>1.323076284966241</v>
       </c>
       <c r="G1777" t="n">
-        <v>4.112633220090752</v>
+        <v>3.878162432191377</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>0.8967763265441863</v>
+        <v>0.5059916800452288</v>
       </c>
       <c r="E1778" t="n">
-        <v>3.440139479002788</v>
+        <v>3.283825620403205</v>
       </c>
       <c r="F1778" t="n">
-        <v>1.720290871681885</v>
+        <v>1.329506225182928</v>
       </c>
       <c r="G1778" t="n">
-        <v>4.113959895707993</v>
+        <v>3.879489107808619</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>0.8985779533831402</v>
+        <v>0.5077933068841827</v>
       </c>
       <c r="E1779" t="n">
-        <v>3.426108691741996</v>
+        <v>3.269794833142412</v>
       </c>
       <c r="F1779" t="n">
-        <v>1.720290871681885</v>
+        <v>1.329506225182928</v>
       </c>
       <c r="G1779" t="n">
-        <v>4.09920845771162</v>
+        <v>3.864737669812245</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>0.8995666351273079</v>
+        <v>0.5087819886283504</v>
       </c>
       <c r="E1780" t="n">
-        <v>3.424617920755335</v>
+        <v>3.268304062155752</v>
       </c>
       <c r="F1780" t="n">
-        <v>1.720290871681885</v>
+        <v>1.329506225182928</v>
       </c>
       <c r="G1780" t="n">
-        <v>4.097322214027291</v>
+        <v>3.862851426127917</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>0.9075629896488465</v>
+        <v>0.516778343149889</v>
       </c>
       <c r="E1781" t="n">
-        <v>3.429790089019791</v>
+        <v>3.273476230420207</v>
       </c>
       <c r="F1781" t="n">
-        <v>1.728287226203424</v>
+        <v>1.337502579704466</v>
       </c>
       <c r="G1781" t="n">
-        <v>4.104093653196055</v>
+        <v>3.86962286529668</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>0.9125467403207552</v>
+        <v>0.5217620938217977</v>
       </c>
       <c r="E1782" t="n">
-        <v>3.443622169879466</v>
+        <v>3.287308311279883</v>
       </c>
       <c r="F1782" t="n">
-        <v>1.733270976875333</v>
+        <v>1.342486330376375</v>
       </c>
       <c r="G1782" t="n">
-        <v>4.118922484190112</v>
+        <v>3.884451696290737</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>0.9189328792703108</v>
+        <v>0.5281482327713533</v>
       </c>
       <c r="E1783" t="n">
-        <v>3.452904828471077</v>
+        <v>3.296590969871494</v>
       </c>
       <c r="F1783" t="n">
-        <v>1.733270976875333</v>
+        <v>1.342486330376375</v>
       </c>
       <c r="G1783" t="n">
-        <v>4.125650687201901</v>
+        <v>3.891179899302526</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>0.9071275289516781</v>
+        <v>0.5163428824527206</v>
       </c>
       <c r="E1784" t="n">
-        <v>3.452198777103166</v>
+        <v>3.295884918503583</v>
       </c>
       <c r="F1784" t="n">
-        <v>1.7214656265567</v>
+        <v>1.330680980057743</v>
       </c>
       <c r="G1784" t="n">
-        <v>4.122583565770264</v>
+        <v>3.888112777870889</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>0.9158593397303444</v>
+        <v>0.5250746932313869</v>
       </c>
       <c r="E1785" t="n">
-        <v>3.461638959024522</v>
+        <v>3.305325100424939</v>
       </c>
       <c r="F1785" t="n">
-        <v>1.730197437335366</v>
+        <v>1.339412790836409</v>
       </c>
       <c r="G1785" t="n">
-        <v>4.133770109847353</v>
+        <v>3.899299321947979</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>0.9221962263747964</v>
+        <v>0.5314115798758389</v>
       </c>
       <c r="E1786" t="n">
-        <v>3.459484532630289</v>
+        <v>3.303170674030706</v>
       </c>
       <c r="F1786" t="n">
-        <v>1.730197437335366</v>
+        <v>1.339412790836409</v>
       </c>
       <c r="G1786" t="n">
-        <v>4.129080928795339</v>
+        <v>3.894610140895964</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>0.9247306741021647</v>
+        <v>0.5339460276032072</v>
       </c>
       <c r="E1787" t="n">
-        <v>3.47046096952343</v>
+        <v>3.314147110923847</v>
       </c>
       <c r="F1787" t="n">
-        <v>1.730197437335366</v>
+        <v>1.339412790836409</v>
       </c>
       <c r="G1787" t="n">
-        <v>4.139043586597532</v>
+        <v>3.904572798698158</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>0.9246547751215601</v>
+        <v>0.5338701286226026</v>
       </c>
       <c r="E1788" t="n">
-        <v>3.462845290124098</v>
+        <v>3.306531431524514</v>
       </c>
       <c r="F1788" t="n">
-        <v>1.730960698024693</v>
+        <v>1.340176051525736</v>
       </c>
       <c r="G1788" t="n">
-        <v>4.131916223204038</v>
+        <v>3.897445435304664</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>0.9141525855622135</v>
+        <v>0.523367939063256</v>
       </c>
       <c r="E1789" t="n">
-        <v>3.436408990090732</v>
+        <v>3.280095131491149</v>
       </c>
       <c r="F1789" t="n">
-        <v>1.720458508465347</v>
+        <v>1.329673861966389</v>
       </c>
       <c r="G1789" t="n">
-        <v>4.103379485258803</v>
+        <v>3.868908697359429</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>0.9123193228830971</v>
+        <v>0.5215346763841396</v>
       </c>
       <c r="E1790" t="n">
-        <v>3.436376524865207</v>
+        <v>3.280062666265624</v>
       </c>
       <c r="F1790" t="n">
-        <v>1.720458508465347</v>
+        <v>1.329673861966389</v>
       </c>
       <c r="G1790" t="n">
-        <v>4.104080325104925</v>
+        <v>3.86960953720555</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>0.9073102078215132</v>
+        <v>0.5165255613225557</v>
       </c>
       <c r="E1791" t="n">
-        <v>3.434889958669433</v>
+        <v>3.27857610006985</v>
       </c>
       <c r="F1791" t="n">
-        <v>1.719463930906812</v>
+        <v>1.328679284407854</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.104000658398664</v>
+        <v>3.869529870499289</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>0.9036046511846986</v>
+        <v>0.5128200046857411</v>
       </c>
       <c r="E1792" t="n">
-        <v>3.432635461255073</v>
+        <v>3.27632160265549</v>
       </c>
       <c r="F1792" t="n">
-        <v>1.717594255649177</v>
+        <v>1.32680960915022</v>
       </c>
       <c r="G1792" t="n">
-        <v>4.102106578484448</v>
+        <v>3.867635790585073</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>0.9048369765420641</v>
+        <v>0.5140523300431066</v>
       </c>
       <c r="E1793" t="n">
-        <v>3.433548243460338</v>
+        <v>3.277234384860755</v>
       </c>
       <c r="F1793" t="n">
-        <v>1.718224632021215</v>
+        <v>1.327439985522257</v>
       </c>
       <c r="G1793" t="n">
-        <v>4.10290465636999</v>
+        <v>3.868433868470615</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>0.9151649735579163</v>
+        <v>0.5243803270589588</v>
       </c>
       <c r="E1794" t="n">
-        <v>3.441809350430892</v>
+        <v>3.28549549183131</v>
       </c>
       <c r="F1794" t="n">
-        <v>1.728552629037067</v>
+        <v>1.337767982538109</v>
       </c>
       <c r="G1794" t="n">
-        <v>4.113231362743715</v>
+        <v>3.87876057484434</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>0.915281308705472</v>
+        <v>0.5244966622065145</v>
       </c>
       <c r="E1795" t="n">
-        <v>3.448376544691751</v>
+        <v>3.292062686092168</v>
       </c>
       <c r="F1795" t="n">
-        <v>1.728668964184623</v>
+        <v>1.337884317685665</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.119821824034084</v>
+        <v>3.88535103613471</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>0.9134358991286045</v>
+        <v>0.522651252629647</v>
       </c>
       <c r="E1796" t="n">
-        <v>3.444612351306393</v>
+        <v>3.28829849270681</v>
       </c>
       <c r="F1796" t="n">
-        <v>1.728668964184623</v>
+        <v>1.337884317685665</v>
       </c>
       <c r="G1796" t="n">
-        <v>4.116795794479473</v>
+        <v>3.882325006580098</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>0.9149343316537033</v>
+        <v>0.5241496851547458</v>
       </c>
       <c r="E1797" t="n">
-        <v>3.445150012177566</v>
+        <v>3.288836153577983</v>
       </c>
       <c r="F1797" t="n">
-        <v>1.730167396709722</v>
+        <v>1.339382750210764</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.117633141855666</v>
+        <v>3.883162353956291</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>0.9068700794609694</v>
+        <v>0.5160854329620119</v>
       </c>
       <c r="E1798" t="n">
-        <v>3.443202289243784</v>
+        <v>3.286888430644201</v>
       </c>
       <c r="F1798" t="n">
-        <v>1.722103144516988</v>
+        <v>1.33131849801803</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.114072568483337</v>
+        <v>3.879601780583963</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>0.905540111999757</v>
+        <v>0.5147554655007995</v>
       </c>
       <c r="E1799" t="n">
-        <v>3.442670302259299</v>
+        <v>3.286356443659716</v>
       </c>
       <c r="F1799" t="n">
-        <v>1.722103144516988</v>
+        <v>1.33131849801803</v>
       </c>
       <c r="G1799" t="n">
-        <v>4.114072568483337</v>
+        <v>3.879601780583963</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>1.133404794733268</v>
+        <v>0.7426201482343107</v>
       </c>
       <c r="E1800" t="n">
-        <v>3.536032648459865</v>
+        <v>3.379718789860283</v>
       </c>
       <c r="F1800" t="n">
-        <v>1.722103144516988</v>
+        <v>1.33131849801803</v>
       </c>
       <c r="G1800" t="n">
-        <v>4.116289041590499</v>
+        <v>3.881818253691125</v>
       </c>
     </row>
     <row r="1801">
@@ -42933,22 +42933,22 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>2.882221957243549</v>
+        <v>2.879277027356208</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>1.401616486749347</v>
+        <v>1.359685177632783</v>
       </c>
       <c r="E1801" t="n">
-        <v>3.650851921611389</v>
+        <v>3.634079397964764</v>
       </c>
       <c r="F1801" t="n">
-        <v>1.722103144516988</v>
+        <v>1.33131849801803</v>
       </c>
       <c r="G1801" t="n">
-        <v>4.123823637935591</v>
+        <v>3.889352850036217</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231204.xlsx
+++ b/tame_output/ON/bt/strategyON_20231204.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
     </row>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>1.359685177632783</v>
+        <v>1.35918162221213</v>
       </c>
       <c r="E1801" t="n">
-        <v>3.634079397964764</v>
+        <v>3.633877975796502</v>
       </c>
       <c r="F1801" t="n">
         <v>1.33131849801803</v>

--- a/tame_output/ON/bt/strategyON_20231204.xlsx
+++ b/tame_output/ON/bt/strategyON_20231204.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -987,22 +987,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.5%</t>
+          <t>448.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-43.3%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>1.35918162221213</v>
+        <v>0.9907217121015275</v>
       </c>
       <c r="E1801" t="n">
-        <v>3.633877975796502</v>
+        <v>3.486494011752261</v>
       </c>
       <c r="F1801" t="n">
         <v>1.33131849801803</v>

--- a/tame_output/ON/bt/strategyON_20231204.xlsx
+++ b/tame_output/ON/bt/strategyON_20231204.xlsx
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255679</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227612</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571589</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708493</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968023</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066011</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.08750545129302</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239773</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.128298755003008</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.13555534016786</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216941</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454037</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780866</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537929</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597765</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527684</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844643</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373819</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502546</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728029</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702053</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487808</v>
+        <v>3.146053372487809</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.15777720152482</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.1572943800687</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714842</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083875</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666732</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097097</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583693</v>
+        <v>3.199276732583694</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
